--- a/Список-2026.xlsx
+++ b/Список-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\МГТУ\ИБМ3\01_МоделиДан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472EEB06-1CE4-4BD6-8045-CBA109DAE753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D987FF9-2A67-4C6D-A379-95F20314104F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="210">
   <si>
     <t>Атаманова Софья</t>
   </si>
@@ -355,32 +355,7 @@
     <t>Антонова Ксения</t>
   </si>
   <si>
-    <r>
-      <t>Антошк</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>и</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ева Тамильяна</t>
-    </r>
+    <t>Антошкиева Тамильяна</t>
   </si>
   <si>
     <t>Анфиногенова Мария</t>
@@ -731,55 +706,10 @@
     <t>М. Митчел "Унесённые ветром"</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">А. Камю "Миф о Сизифе", "Бунтующий человек"; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ф. Достоевский "Братья Карамазовы"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>; Г. Гессе</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Дж. Д. Сэлинджер "Над пропостью во ржи"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>; Э. Вейр "Проект Аве Мария" (англ.)</t>
-    </r>
+    <t>А. Камю "Миф о Сизифе", "Бунтующий человек"; Ф. Достоевский "Братья Карамазовы"; Г. Гессе</t>
+  </si>
+  <si>
+    <t>Дж. Д. Сэлинджер "Над пропостью во ржи"; Э. Вейр "Проект Аве Мария" (англ.)</t>
   </si>
 </sst>
 </file>
@@ -837,15 +767,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -878,7 +799,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -886,7 +807,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -1011,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1074,16 +1004,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1092,11 +1022,32 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1110,34 +1061,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1243,154 +1176,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
@@ -1643,6 +1428,154 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1689,34 +1622,34 @@
     <cacheField name="[Measures].[Число элементов в столбце Имя]" caption="Число элементов в столбце Имя" numFmtId="0" hierarchy="22" level="32767"/>
   </cacheFields>
   <cacheHierarchies count="25">
-    <cacheHierarchy uniqueName="[Список].[№]" caption="№" attribute="1" defaultMemberUniqueName="[Список].[№].[All]" allUniqueName="[Список].[№].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Фамилия, имя]" caption="Фамилия, имя" attribute="1" defaultMemberUniqueName="[Список].[Фамилия, имя].[All]" allUniqueName="[Список].[Фамилия, имя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Список].[Имя].[All]" allUniqueName="[Список].[Имя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+    <cacheHierarchy uniqueName="[Список].[№]" caption="№" attribute="1" defaultMemberUniqueName="[Список].[№].[All]" allUniqueName="[Список].[№].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Фамилия, имя]" caption="Фамилия, имя" attribute="1" defaultMemberUniqueName="[Список].[Фамилия, имя].[All]" allUniqueName="[Список].[Фамилия, имя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Список].[Имя].[All]" allUniqueName="[Список].[Имя].[All]" dimensionUniqueName="[Список]" count="2" memberValueDatatype="130" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
         <fieldUsage x="0"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Список].[Пол]" caption="Пол" attribute="1" defaultMemberUniqueName="[Список].[Пол].[All]" allUniqueName="[Список].[Пол].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Вар. ЛР]" caption="Вар. ЛР" attribute="1" defaultMemberUniqueName="[Список].[Вар. ЛР].[All]" allUniqueName="[Список].[Вар. ЛР].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[08.сен]" caption="08.сен" attribute="1" defaultMemberUniqueName="[Список].[08.сен].[All]" allUniqueName="[Список].[08.сен].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[22.сен]" caption="22.сен" attribute="1" defaultMemberUniqueName="[Список].[22.сен].[All]" allUniqueName="[Список].[22.сен].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[06.окт]" caption="06.окт" attribute="1" defaultMemberUniqueName="[Список].[06.окт].[All]" allUniqueName="[Список].[06.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[20.окт]" caption="20.окт" attribute="1" defaultMemberUniqueName="[Список].[20.окт].[All]" allUniqueName="[Список].[20.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[17.ноя]" caption="17.ноя" attribute="1" defaultMemberUniqueName="[Список].[17.ноя].[All]" allUniqueName="[Список].[17.ноя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[01.дек]" caption="01.дек" attribute="1" defaultMemberUniqueName="[Список].[01.дек].[All]" allUniqueName="[Список].[01.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[15.дек]" caption="15.дек" attribute="1" defaultMemberUniqueName="[Список].[15.дек].[All]" allUniqueName="[Список].[15.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[22.дек]" caption="22.дек" attribute="1" defaultMemberUniqueName="[Список].[22.дек].[All]" allUniqueName="[Список].[22.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Встреч]" caption="Встреч" attribute="1" defaultMemberUniqueName="[Список].[Встреч].[All]" allUniqueName="[Список].[Встреч].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[27.окт]" caption="27.окт" attribute="1" defaultMemberUniqueName="[Список].[27.окт].[All]" allUniqueName="[Список].[27.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Баллы1]" caption="Баллы1" attribute="1" defaultMemberUniqueName="[Список].[Баллы1].[All]" allUniqueName="[Список].[Баллы1].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Баллы2]" caption="Баллы2" attribute="1" defaultMemberUniqueName="[Список].[Баллы2].[All]" allUniqueName="[Список].[Баллы2].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[ДЗ]" caption="ДЗ" attribute="1" defaultMemberUniqueName="[Список].[ДЗ].[All]" allUniqueName="[Список].[ДЗ].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Таблица3].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Таблица3].[Имя].[All]" allUniqueName="[Таблица3].[Имя].[All]" dimensionUniqueName="[Таблица3]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Список]" caption="__XL_Count Список" measure="1" displayFolder="" measureGroup="Список" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Таблица3]" caption="__XL_Count Таблица3" measure="1" displayFolder="" measureGroup="Таблица3" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя]" caption="Число элементов в столбце Имя" measure="1" displayFolder="" measureGroup="Список" count="0" oneField="1" hidden="1">
+    <cacheHierarchy uniqueName="[Список].[Пол]" caption="Пол" attribute="1" defaultMemberUniqueName="[Список].[Пол].[All]" allUniqueName="[Список].[Пол].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Вар. ЛР]" caption="Вар. ЛР" attribute="1" defaultMemberUniqueName="[Список].[Вар. ЛР].[All]" allUniqueName="[Список].[Вар. ЛР].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[08.сен]" caption="08.сен" attribute="1" defaultMemberUniqueName="[Список].[08.сен].[All]" allUniqueName="[Список].[08.сен].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[22.сен]" caption="22.сен" attribute="1" defaultMemberUniqueName="[Список].[22.сен].[All]" allUniqueName="[Список].[22.сен].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[06.окт]" caption="06.окт" attribute="1" defaultMemberUniqueName="[Список].[06.окт].[All]" allUniqueName="[Список].[06.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[20.окт]" caption="20.окт" attribute="1" defaultMemberUniqueName="[Список].[20.окт].[All]" allUniqueName="[Список].[20.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[17.ноя]" caption="17.ноя" attribute="1" defaultMemberUniqueName="[Список].[17.ноя].[All]" allUniqueName="[Список].[17.ноя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[01.дек]" caption="01.дек" attribute="1" defaultMemberUniqueName="[Список].[01.дек].[All]" allUniqueName="[Список].[01.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[15.дек]" caption="15.дек" attribute="1" defaultMemberUniqueName="[Список].[15.дек].[All]" allUniqueName="[Список].[15.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[22.дек]" caption="22.дек" attribute="1" defaultMemberUniqueName="[Список].[22.дек].[All]" allUniqueName="[Список].[22.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Встреч]" caption="Встреч" attribute="1" defaultMemberUniqueName="[Список].[Встреч].[All]" allUniqueName="[Список].[Встреч].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[27.окт]" caption="27.окт" attribute="1" defaultMemberUniqueName="[Список].[27.окт].[All]" allUniqueName="[Список].[27.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Баллы1]" caption="Баллы1" attribute="1" defaultMemberUniqueName="[Список].[Баллы1].[All]" allUniqueName="[Список].[Баллы1].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Баллы2]" caption="Баллы2" attribute="1" defaultMemberUniqueName="[Список].[Баллы2].[All]" allUniqueName="[Список].[Баллы2].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[ДЗ]" caption="ДЗ" attribute="1" defaultMemberUniqueName="[Список].[ДЗ].[All]" allUniqueName="[Список].[ДЗ].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Таблица3].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Таблица3].[Имя].[All]" allUniqueName="[Таблица3].[Имя].[All]" dimensionUniqueName="[Таблица3]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Список]" caption="__XL_Count Список" measure="1" measureGroup="Список" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Таблица3]" caption="__XL_Count Таблица3" measure="1" measureGroup="Таблица3" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя]" caption="Число элементов в столбце Имя" measure="1" measureGroup="Список" count="0" oneField="1" hidden="1">
       <fieldsUsage count="1">
         <fieldUsage x="1"/>
       </fieldsUsage>
@@ -1726,14 +1659,14 @@
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Пол]" caption="Число элементов в столбце Пол" measure="1" displayFolder="" measureGroup="Список" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Пол]" caption="Число элементов в столбце Пол" measure="1" measureGroup="Список" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="3"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя 2]" caption="Число элементов в столбце Имя 2" measure="1" displayFolder="" measureGroup="Таблица3" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя 2]" caption="Число элементов в столбце Имя 2" measure="1" measureGroup="Таблица3" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="18"/>
@@ -1776,41 +1709,41 @@
     <cacheField name="[Measures].[Число элементов в столбце Пол]" caption="Число элементов в столбце Пол" numFmtId="0" hierarchy="23" level="32767"/>
   </cacheFields>
   <cacheHierarchies count="25">
-    <cacheHierarchy uniqueName="[Список].[№]" caption="№" attribute="1" defaultMemberUniqueName="[Список].[№].[All]" allUniqueName="[Список].[№].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Фамилия, имя]" caption="Фамилия, имя" attribute="1" defaultMemberUniqueName="[Список].[Фамилия, имя].[All]" allUniqueName="[Список].[Фамилия, имя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Список].[Имя].[All]" allUniqueName="[Список].[Имя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Пол]" caption="Пол" attribute="1" defaultMemberUniqueName="[Список].[Пол].[All]" allUniqueName="[Список].[Пол].[All]" dimensionUniqueName="[Список]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+    <cacheHierarchy uniqueName="[Список].[№]" caption="№" attribute="1" defaultMemberUniqueName="[Список].[№].[All]" allUniqueName="[Список].[№].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Фамилия, имя]" caption="Фамилия, имя" attribute="1" defaultMemberUniqueName="[Список].[Фамилия, имя].[All]" allUniqueName="[Список].[Фамилия, имя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Список].[Имя].[All]" allUniqueName="[Список].[Имя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Пол]" caption="Пол" attribute="1" defaultMemberUniqueName="[Список].[Пол].[All]" allUniqueName="[Список].[Пол].[All]" dimensionUniqueName="[Список]" count="2" memberValueDatatype="130" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
         <fieldUsage x="0"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Список].[Вар. ЛР]" caption="Вар. ЛР" attribute="1" defaultMemberUniqueName="[Список].[Вар. ЛР].[All]" allUniqueName="[Список].[Вар. ЛР].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[08.сен]" caption="08.сен" attribute="1" defaultMemberUniqueName="[Список].[08.сен].[All]" allUniqueName="[Список].[08.сен].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[22.сен]" caption="22.сен" attribute="1" defaultMemberUniqueName="[Список].[22.сен].[All]" allUniqueName="[Список].[22.сен].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[06.окт]" caption="06.окт" attribute="1" defaultMemberUniqueName="[Список].[06.окт].[All]" allUniqueName="[Список].[06.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[20.окт]" caption="20.окт" attribute="1" defaultMemberUniqueName="[Список].[20.окт].[All]" allUniqueName="[Список].[20.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[17.ноя]" caption="17.ноя" attribute="1" defaultMemberUniqueName="[Список].[17.ноя].[All]" allUniqueName="[Список].[17.ноя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[01.дек]" caption="01.дек" attribute="1" defaultMemberUniqueName="[Список].[01.дек].[All]" allUniqueName="[Список].[01.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[15.дек]" caption="15.дек" attribute="1" defaultMemberUniqueName="[Список].[15.дек].[All]" allUniqueName="[Список].[15.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[22.дек]" caption="22.дек" attribute="1" defaultMemberUniqueName="[Список].[22.дек].[All]" allUniqueName="[Список].[22.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Встреч]" caption="Встреч" attribute="1" defaultMemberUniqueName="[Список].[Встреч].[All]" allUniqueName="[Список].[Встреч].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[27.окт]" caption="27.окт" attribute="1" defaultMemberUniqueName="[Список].[27.окт].[All]" allUniqueName="[Список].[27.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Баллы1]" caption="Баллы1" attribute="1" defaultMemberUniqueName="[Список].[Баллы1].[All]" allUniqueName="[Список].[Баллы1].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Баллы2]" caption="Баллы2" attribute="1" defaultMemberUniqueName="[Список].[Баллы2].[All]" allUniqueName="[Список].[Баллы2].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[ДЗ]" caption="ДЗ" attribute="1" defaultMemberUniqueName="[Список].[ДЗ].[All]" allUniqueName="[Список].[ДЗ].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Таблица3].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Таблица3].[Имя].[All]" allUniqueName="[Таблица3].[Имя].[All]" dimensionUniqueName="[Таблица3]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Список]" caption="__XL_Count Список" measure="1" displayFolder="" measureGroup="Список" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Таблица3]" caption="__XL_Count Таблица3" measure="1" displayFolder="" measureGroup="Таблица3" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя]" caption="Число элементов в столбце Имя" measure="1" displayFolder="" measureGroup="Список" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Список].[Вар. ЛР]" caption="Вар. ЛР" attribute="1" defaultMemberUniqueName="[Список].[Вар. ЛР].[All]" allUniqueName="[Список].[Вар. ЛР].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[08.сен]" caption="08.сен" attribute="1" defaultMemberUniqueName="[Список].[08.сен].[All]" allUniqueName="[Список].[08.сен].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[22.сен]" caption="22.сен" attribute="1" defaultMemberUniqueName="[Список].[22.сен].[All]" allUniqueName="[Список].[22.сен].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[06.окт]" caption="06.окт" attribute="1" defaultMemberUniqueName="[Список].[06.окт].[All]" allUniqueName="[Список].[06.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[20.окт]" caption="20.окт" attribute="1" defaultMemberUniqueName="[Список].[20.окт].[All]" allUniqueName="[Список].[20.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[17.ноя]" caption="17.ноя" attribute="1" defaultMemberUniqueName="[Список].[17.ноя].[All]" allUniqueName="[Список].[17.ноя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[01.дек]" caption="01.дек" attribute="1" defaultMemberUniqueName="[Список].[01.дек].[All]" allUniqueName="[Список].[01.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[15.дек]" caption="15.дек" attribute="1" defaultMemberUniqueName="[Список].[15.дек].[All]" allUniqueName="[Список].[15.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[22.дек]" caption="22.дек" attribute="1" defaultMemberUniqueName="[Список].[22.дек].[All]" allUniqueName="[Список].[22.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Встреч]" caption="Встреч" attribute="1" defaultMemberUniqueName="[Список].[Встреч].[All]" allUniqueName="[Список].[Встреч].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[27.окт]" caption="27.окт" attribute="1" defaultMemberUniqueName="[Список].[27.окт].[All]" allUniqueName="[Список].[27.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Баллы1]" caption="Баллы1" attribute="1" defaultMemberUniqueName="[Список].[Баллы1].[All]" allUniqueName="[Список].[Баллы1].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Баллы2]" caption="Баллы2" attribute="1" defaultMemberUniqueName="[Список].[Баллы2].[All]" allUniqueName="[Список].[Баллы2].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[ДЗ]" caption="ДЗ" attribute="1" defaultMemberUniqueName="[Список].[ДЗ].[All]" allUniqueName="[Список].[ДЗ].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Таблица3].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Таблица3].[Имя].[All]" allUniqueName="[Таблица3].[Имя].[All]" dimensionUniqueName="[Таблица3]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Список]" caption="__XL_Count Список" measure="1" measureGroup="Список" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Таблица3]" caption="__XL_Count Таблица3" measure="1" measureGroup="Таблица3" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя]" caption="Число элементов в столбце Имя" measure="1" measureGroup="Список" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="2"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Пол]" caption="Число элементов в столбце Пол" measure="1" displayFolder="" measureGroup="Список" count="0" oneField="1" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Пол]" caption="Число элементов в столбце Пол" measure="1" measureGroup="Список" count="0" oneField="1" hidden="1">
       <fieldsUsage count="1">
         <fieldUsage x="1"/>
       </fieldsUsage>
@@ -1820,7 +1753,7 @@
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя 2]" caption="Число элементов в столбце Имя 2" measure="1" displayFolder="" measureGroup="Таблица3" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя 2]" caption="Число элементов в столбце Имя 2" measure="1" measureGroup="Таблица3" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="18"/>
@@ -1877,48 +1810,48 @@
     <cacheField name="[Measures].[Число элементов в столбце Имя 2]" caption="Число элементов в столбце Имя 2" numFmtId="0" hierarchy="24" level="32767"/>
   </cacheFields>
   <cacheHierarchies count="25">
-    <cacheHierarchy uniqueName="[Список].[№]" caption="№" attribute="1" defaultMemberUniqueName="[Список].[№].[All]" allUniqueName="[Список].[№].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Фамилия, имя]" caption="Фамилия, имя" attribute="1" defaultMemberUniqueName="[Список].[Фамилия, имя].[All]" allUniqueName="[Список].[Фамилия, имя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Список].[Имя].[All]" allUniqueName="[Список].[Имя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Пол]" caption="Пол" attribute="1" defaultMemberUniqueName="[Список].[Пол].[All]" allUniqueName="[Список].[Пол].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Вар. ЛР]" caption="Вар. ЛР" attribute="1" defaultMemberUniqueName="[Список].[Вар. ЛР].[All]" allUniqueName="[Список].[Вар. ЛР].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[08.сен]" caption="08.сен" attribute="1" defaultMemberUniqueName="[Список].[08.сен].[All]" allUniqueName="[Список].[08.сен].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[22.сен]" caption="22.сен" attribute="1" defaultMemberUniqueName="[Список].[22.сен].[All]" allUniqueName="[Список].[22.сен].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[06.окт]" caption="06.окт" attribute="1" defaultMemberUniqueName="[Список].[06.окт].[All]" allUniqueName="[Список].[06.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[20.окт]" caption="20.окт" attribute="1" defaultMemberUniqueName="[Список].[20.окт].[All]" allUniqueName="[Список].[20.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[17.ноя]" caption="17.ноя" attribute="1" defaultMemberUniqueName="[Список].[17.ноя].[All]" allUniqueName="[Список].[17.ноя].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[01.дек]" caption="01.дек" attribute="1" defaultMemberUniqueName="[Список].[01.дек].[All]" allUniqueName="[Список].[01.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[15.дек]" caption="15.дек" attribute="1" defaultMemberUniqueName="[Список].[15.дек].[All]" allUniqueName="[Список].[15.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[22.дек]" caption="22.дек" attribute="1" defaultMemberUniqueName="[Список].[22.дек].[All]" allUniqueName="[Список].[22.дек].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Встреч]" caption="Встреч" attribute="1" defaultMemberUniqueName="[Список].[Встреч].[All]" allUniqueName="[Список].[Встреч].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[27.окт]" caption="27.окт" attribute="1" defaultMemberUniqueName="[Список].[27.окт].[All]" allUniqueName="[Список].[27.окт].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Баллы1]" caption="Баллы1" attribute="1" defaultMemberUniqueName="[Список].[Баллы1].[All]" allUniqueName="[Список].[Баллы1].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[Баллы2]" caption="Баллы2" attribute="1" defaultMemberUniqueName="[Список].[Баллы2].[All]" allUniqueName="[Список].[Баллы2].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Список].[ДЗ]" caption="ДЗ" attribute="1" defaultMemberUniqueName="[Список].[ДЗ].[All]" allUniqueName="[Список].[ДЗ].[All]" dimensionUniqueName="[Список]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Таблица3].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Таблица3].[Имя].[All]" allUniqueName="[Таблица3].[Имя].[All]" dimensionUniqueName="[Таблица3]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+    <cacheHierarchy uniqueName="[Список].[№]" caption="№" attribute="1" defaultMemberUniqueName="[Список].[№].[All]" allUniqueName="[Список].[№].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Фамилия, имя]" caption="Фамилия, имя" attribute="1" defaultMemberUniqueName="[Список].[Фамилия, имя].[All]" allUniqueName="[Список].[Фамилия, имя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Список].[Имя].[All]" allUniqueName="[Список].[Имя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Пол]" caption="Пол" attribute="1" defaultMemberUniqueName="[Список].[Пол].[All]" allUniqueName="[Список].[Пол].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Вар. ЛР]" caption="Вар. ЛР" attribute="1" defaultMemberUniqueName="[Список].[Вар. ЛР].[All]" allUniqueName="[Список].[Вар. ЛР].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[08.сен]" caption="08.сен" attribute="1" defaultMemberUniqueName="[Список].[08.сен].[All]" allUniqueName="[Список].[08.сен].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[22.сен]" caption="22.сен" attribute="1" defaultMemberUniqueName="[Список].[22.сен].[All]" allUniqueName="[Список].[22.сен].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[06.окт]" caption="06.окт" attribute="1" defaultMemberUniqueName="[Список].[06.окт].[All]" allUniqueName="[Список].[06.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[20.окт]" caption="20.окт" attribute="1" defaultMemberUniqueName="[Список].[20.окт].[All]" allUniqueName="[Список].[20.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[17.ноя]" caption="17.ноя" attribute="1" defaultMemberUniqueName="[Список].[17.ноя].[All]" allUniqueName="[Список].[17.ноя].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[01.дек]" caption="01.дек" attribute="1" defaultMemberUniqueName="[Список].[01.дек].[All]" allUniqueName="[Список].[01.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[15.дек]" caption="15.дек" attribute="1" defaultMemberUniqueName="[Список].[15.дек].[All]" allUniqueName="[Список].[15.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[22.дек]" caption="22.дек" attribute="1" defaultMemberUniqueName="[Список].[22.дек].[All]" allUniqueName="[Список].[22.дек].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Встреч]" caption="Встреч" attribute="1" defaultMemberUniqueName="[Список].[Встреч].[All]" allUniqueName="[Список].[Встреч].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[27.окт]" caption="27.окт" attribute="1" defaultMemberUniqueName="[Список].[27.окт].[All]" allUniqueName="[Список].[27.окт].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Баллы1]" caption="Баллы1" attribute="1" defaultMemberUniqueName="[Список].[Баллы1].[All]" allUniqueName="[Список].[Баллы1].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[Баллы2]" caption="Баллы2" attribute="1" defaultMemberUniqueName="[Список].[Баллы2].[All]" allUniqueName="[Список].[Баллы2].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Список].[ДЗ]" caption="ДЗ" attribute="1" defaultMemberUniqueName="[Список].[ДЗ].[All]" allUniqueName="[Список].[ДЗ].[All]" dimensionUniqueName="[Список]" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Таблица3].[Имя]" caption="Имя" attribute="1" defaultMemberUniqueName="[Таблица3].[Имя].[All]" allUniqueName="[Таблица3].[Имя].[All]" dimensionUniqueName="[Таблица3]" count="2" memberValueDatatype="130" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
         <fieldUsage x="0"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Список]" caption="__XL_Count Список" measure="1" displayFolder="" measureGroup="Список" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Таблица3]" caption="__XL_Count Таблица3" measure="1" displayFolder="" measureGroup="Таблица3" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя]" caption="Число элементов в столбце Имя" measure="1" displayFolder="" measureGroup="Список" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Список]" caption="__XL_Count Список" measure="1" measureGroup="Список" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Таблица3]" caption="__XL_Count Таблица3" measure="1" measureGroup="Таблица3" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя]" caption="Число элементов в столбце Имя" measure="1" measureGroup="Список" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="2"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Пол]" caption="Число элементов в столбце Пол" measure="1" displayFolder="" measureGroup="Список" count="0" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Пол]" caption="Число элементов в столбце Пол" measure="1" measureGroup="Список" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="3"/>
         </ext>
       </extLst>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя 2]" caption="Число элементов в столбце Имя 2" measure="1" displayFolder="" measureGroup="Таблица3" count="0" oneField="1" hidden="1">
+    <cacheHierarchy uniqueName="[Measures].[Число элементов в столбце Имя 2]" caption="Число элементов в столбце Имя 2" measure="1" measureGroup="Таблица3" count="0" oneField="1" hidden="1">
       <fieldsUsage count="1">
         <fieldUsage x="1"/>
       </fieldsUsage>
@@ -2213,7 +2146,7 @@
     <dataField name="Число элементов в столбце Имя" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="19">
-    <format dxfId="86">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2222,7 +2155,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="85">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2231,7 +2164,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="84">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2240,7 +2173,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="83">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2249,7 +2182,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2258,7 +2191,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="81">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2267,7 +2200,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="46">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2276,7 +2209,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="79">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2285,7 +2218,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="78">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2294,7 +2227,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="77">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2303,7 +2236,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2312,7 +2245,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="75">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2321,7 +2254,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2330,7 +2263,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2339,7 +2272,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2348,7 +2281,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="4">
@@ -2360,7 +2293,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2369,7 +2302,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="4">
@@ -2381,7 +2314,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
@@ -2471,7 +2404,7 @@
     <dataField name="Число элементов в столбце Пол" fld="1" subtotal="count" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="9"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="67">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -2525,117 +2458,111 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1B9CDCE8-376C-4F6F-A47F-34521FF715C6}" name="Список35" displayName="Список35" ref="B5:AI38" totalsRowCount="1">
   <autoFilter ref="B5:AI37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:O33">
-    <sortCondition ref="B5:B33"/>
-  </sortState>
   <tableColumns count="34">
-    <tableColumn id="1" xr3:uid="{958D3CE3-DF36-46CA-A124-B85A503DF7C3}" name="№" dataDxfId="66" totalsRowDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{21BE5498-42F8-44F6-BB8B-EA42F84ADC3E}" name="Фамилия, имя" dataDxfId="65" totalsRowDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{DE4AB761-E0AC-408E-B001-5121C7FBE889}" name="Имя" dataDxfId="64" totalsRowDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{DC6CA474-70D9-488B-A84F-0A21CA2B1190}" name="Пол" dataDxfId="63" totalsRowDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{44B84C7C-6809-441D-AB04-4156BF082B0A}" name="Вар. ЛР" dataDxfId="62" totalsRowDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{3F34C439-4AA8-4327-9748-46E64109AEF1}" name="02.сен" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="27">
+    <tableColumn id="1" xr3:uid="{958D3CE3-DF36-46CA-A124-B85A503DF7C3}" name="№" dataDxfId="98" totalsRowDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{21BE5498-42F8-44F6-BB8B-EA42F84ADC3E}" name="Фамилия, имя" dataDxfId="97" totalsRowDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{DE4AB761-E0AC-408E-B001-5121C7FBE889}" name="Имя" dataDxfId="96" totalsRowDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{DC6CA474-70D9-488B-A84F-0A21CA2B1190}" name="Пол" dataDxfId="95" totalsRowDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{44B84C7C-6809-441D-AB04-4156BF082B0A}" name="Вар. ЛР" dataDxfId="94" totalsRowDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{3F34C439-4AA8-4327-9748-46E64109AEF1}" name="02.сен" totalsRowFunction="custom" dataDxfId="93" totalsRowDxfId="27">
       <totalsRowFormula>COUNTA(Список35[02.сен])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C5EA210A-8AED-4F1D-9BB6-8141384A7ED4}" name="16.сен" totalsRowFunction="custom" dataDxfId="60" totalsRowDxfId="26">
+    <tableColumn id="6" xr3:uid="{C5EA210A-8AED-4F1D-9BB6-8141384A7ED4}" name="16.сен" totalsRowFunction="custom" dataDxfId="92" totalsRowDxfId="26">
       <totalsRowFormula>COUNTA(Список35[16.сен])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B21FDCDC-89AD-485A-9AF0-5136CCB9912C}" name="30.сен" totalsRowFunction="custom" dataDxfId="59" totalsRowDxfId="25">
+    <tableColumn id="7" xr3:uid="{B21FDCDC-89AD-485A-9AF0-5136CCB9912C}" name="30.сен" totalsRowFunction="custom" dataDxfId="91" totalsRowDxfId="25">
       <totalsRowFormula>COUNTA(Список35[30.сен])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6A100862-1981-4533-ADAD-23BD1AF89D4D}" name="14.окт" totalsRowFunction="custom" dataDxfId="58" totalsRowDxfId="24">
+    <tableColumn id="8" xr3:uid="{6A100862-1981-4533-ADAD-23BD1AF89D4D}" name="14.окт" totalsRowFunction="custom" dataDxfId="90" totalsRowDxfId="24">
       <totalsRowFormula>COUNTA(Список35[14.окт])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{397ED156-1301-4756-90AB-0B6BC97BBE22}" name="28.окт" totalsRowFunction="custom" dataDxfId="57" totalsRowDxfId="23">
+    <tableColumn id="11" xr3:uid="{397ED156-1301-4756-90AB-0B6BC97BBE22}" name="28.окт" totalsRowFunction="custom" dataDxfId="89" totalsRowDxfId="23">
       <totalsRowFormula>COUNTA(Список35[28.окт])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{AB088FA0-F829-4AA2-863D-7B259A11FB8E}" name="11.дек" totalsRowFunction="custom" dataDxfId="56" totalsRowDxfId="22">
+    <tableColumn id="12" xr3:uid="{AB088FA0-F829-4AA2-863D-7B259A11FB8E}" name="11.дек" totalsRowFunction="custom" dataDxfId="88" totalsRowDxfId="22">
       <totalsRowFormula>COUNTA(Список35[11.дек])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E36B2DC4-67DF-4F03-A9BE-619599C5F369}" name="25.дек" totalsRowFunction="custom" dataDxfId="55" totalsRowDxfId="21">
+    <tableColumn id="13" xr3:uid="{E36B2DC4-67DF-4F03-A9BE-619599C5F369}" name="25.дек" totalsRowFunction="custom" dataDxfId="87" totalsRowDxfId="21">
       <totalsRowFormula>COUNTA(Список35[25.дек])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{3D8BEBA8-6BD8-4260-B67F-EAE9146366B5}" name="Лекции" dataDxfId="54" totalsRowDxfId="20">
+    <tableColumn id="15" xr3:uid="{3D8BEBA8-6BD8-4260-B67F-EAE9146366B5}" name="Лекции" dataDxfId="86" totalsRowDxfId="20">
       <calculatedColumnFormula>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0262A76C-5053-45D8-B41E-5F3EFE47382B}" name="РК1" totalsRowFunction="countNums" dataDxfId="53" totalsRowDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{E4C90AFA-E5CD-4B6A-A496-242129B2E994}" name="РК2" totalsRowFunction="countNums" dataDxfId="52" totalsRowDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{BA523250-0BB3-4727-BFD1-52C03A669A27}" name="РК3" totalsRowFunction="countNums" dataDxfId="51" totalsRowDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{3A6F8A31-E54A-4649-A700-ABD104EECE04}" name="ДЗ" totalsRowFunction="countNums" dataDxfId="50" totalsRowDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{6521CEE6-C7BE-4AB2-A139-E2CEEC1FAF30}" name="Теория" dataDxfId="49" totalsRowDxfId="15">
+    <tableColumn id="16" xr3:uid="{0262A76C-5053-45D8-B41E-5F3EFE47382B}" name="РК1" totalsRowFunction="countNums" dataDxfId="85" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{E4C90AFA-E5CD-4B6A-A496-242129B2E994}" name="РК2" totalsRowFunction="countNums" dataDxfId="84" totalsRowDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{BA523250-0BB3-4727-BFD1-52C03A669A27}" name="РК3" totalsRowFunction="countNums" dataDxfId="83" totalsRowDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{3A6F8A31-E54A-4649-A700-ABD104EECE04}" name="ДЗ" totalsRowFunction="countNums" dataDxfId="82" totalsRowDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{6521CEE6-C7BE-4AB2-A139-E2CEEC1FAF30}" name="Теория" dataDxfId="81" totalsRowDxfId="15">
       <calculatedColumnFormula>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{8B821441-1EEC-4DF0-9D6A-5BDA72942403}" name="09.сен" totalsRowFunction="custom" dataDxfId="48" totalsRowDxfId="14">
+    <tableColumn id="20" xr3:uid="{8B821441-1EEC-4DF0-9D6A-5BDA72942403}" name="09.сен" totalsRowFunction="custom" dataDxfId="80" totalsRowDxfId="14">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{17B88E00-65F1-4457-BA22-E0FBEC945F7B}" name="23.сен" totalsRowFunction="custom" dataDxfId="47" totalsRowDxfId="13">
+    <tableColumn id="21" xr3:uid="{17B88E00-65F1-4457-BA22-E0FBEC945F7B}" name="23.сен" totalsRowFunction="custom" dataDxfId="79" totalsRowDxfId="13">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{0F5B0088-A5FE-4DC0-AD62-F378C41789BE}" name="07.окт" totalsRowFunction="custom" dataDxfId="46" totalsRowDxfId="12">
+    <tableColumn id="22" xr3:uid="{0F5B0088-A5FE-4DC0-AD62-F378C41789BE}" name="07.окт" totalsRowFunction="custom" dataDxfId="78" totalsRowDxfId="12">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{E34AE642-6959-43C7-8C63-274E6455B1F0}" name="21.окт" totalsRowFunction="custom" dataDxfId="45" totalsRowDxfId="11">
+    <tableColumn id="23" xr3:uid="{E34AE642-6959-43C7-8C63-274E6455B1F0}" name="21.окт" totalsRowFunction="custom" dataDxfId="77" totalsRowDxfId="11">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{55352D33-2545-425C-BFBF-5FD7B604D215}" name="18.ноя" totalsRowFunction="custom" dataDxfId="44" totalsRowDxfId="10">
+    <tableColumn id="24" xr3:uid="{55352D33-2545-425C-BFBF-5FD7B604D215}" name="18.ноя" totalsRowFunction="custom" dataDxfId="76" totalsRowDxfId="10">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{A9F8128D-F247-4C47-B484-18878537FF22}" name="02.дек" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="9">
+    <tableColumn id="25" xr3:uid="{A9F8128D-F247-4C47-B484-18878537FF22}" name="02.дек" totalsRowFunction="custom" dataDxfId="75" totalsRowDxfId="9">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{785C4B91-C255-4AA7-9765-AD03EAF94526}" name="16.дек" totalsRowFunction="custom" dataDxfId="42" totalsRowDxfId="8">
+    <tableColumn id="26" xr3:uid="{785C4B91-C255-4AA7-9765-AD03EAF94526}" name="16.дек" totalsRowFunction="custom" dataDxfId="74" totalsRowDxfId="8">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{03D2E624-EA46-4485-8D84-7DEA20D030F7}" name="30.дек" totalsRowFunction="custom" dataDxfId="41" totalsRowDxfId="7">
+    <tableColumn id="27" xr3:uid="{03D2E624-EA46-4485-8D84-7DEA20D030F7}" name="30.дек" totalsRowFunction="custom" dataDxfId="73" totalsRowDxfId="7">
       <totalsRowFormula>COUNTA(#REF!)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{A6F037A1-758D-47CE-B1D2-0B052CFF9CFD}" name="Лабы" dataDxfId="40" totalsRowDxfId="6">
+    <tableColumn id="28" xr3:uid="{A6F037A1-758D-47CE-B1D2-0B052CFF9CFD}" name="Лабы" dataDxfId="72" totalsRowDxfId="6">
       <calculatedColumnFormula>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{D5EEC82C-5A0A-4AF5-8C0C-ED1AC79A97E2}" name="Отч1" totalsRowFunction="custom" dataDxfId="39" totalsRowDxfId="5">
+    <tableColumn id="29" xr3:uid="{D5EEC82C-5A0A-4AF5-8C0C-ED1AC79A97E2}" name="Отч1" totalsRowFunction="custom" dataDxfId="71" totalsRowDxfId="5">
       <calculatedColumnFormula>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</calculatedColumnFormula>
       <totalsRowFormula>COUNTIF(Список35[Отч1],"&lt;&gt;0")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{36593401-E942-41AF-9243-5AC2E5D2506E}" name="Отч2" totalsRowFunction="custom" dataDxfId="38" totalsRowDxfId="4">
+    <tableColumn id="30" xr3:uid="{36593401-E942-41AF-9243-5AC2E5D2506E}" name="Отч2" totalsRowFunction="custom" dataDxfId="70" totalsRowDxfId="4">
       <calculatedColumnFormula>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</calculatedColumnFormula>
       <totalsRowFormula>COUNTIF(Список35[Отч2],"&lt;&gt;0")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{8BCA4CB0-E93C-4375-A81C-5F367566B6E7}" name="Отч3" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="3">
+    <tableColumn id="31" xr3:uid="{8BCA4CB0-E93C-4375-A81C-5F367566B6E7}" name="Отч3" totalsRowFunction="custom" dataDxfId="69" totalsRowDxfId="3">
       <calculatedColumnFormula>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</calculatedColumnFormula>
       <totalsRowFormula>COUNTIF(Список35[Отч3],"&lt;&gt;0")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{46CA83D2-E910-4A50-91EF-66C3A41C422D}" name="Отч4" totalsRowFunction="custom" dataDxfId="36" totalsRowDxfId="2">
+    <tableColumn id="32" xr3:uid="{46CA83D2-E910-4A50-91EF-66C3A41C422D}" name="Отч4" totalsRowFunction="custom" dataDxfId="68" totalsRowDxfId="2">
       <calculatedColumnFormula>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</calculatedColumnFormula>
       <totalsRowFormula>COUNTIF(Список35[Отч4],"&lt;&gt;0")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{EF5FFCD7-60F6-4561-9914-D1C15E750F40}" name="Практика" dataDxfId="35" totalsRowDxfId="1">
+    <tableColumn id="33" xr3:uid="{EF5FFCD7-60F6-4561-9914-D1C15E750F40}" name="Практика" dataDxfId="67" totalsRowDxfId="1">
       <calculatedColumnFormula>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{CC9FBEAE-772D-4FB1-BC51-15A3B9362BEB}" name="Итог" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="0">
+    <tableColumn id="34" xr3:uid="{CC9FBEAE-772D-4FB1-BC51-15A3B9362BEB}" name="Итог" dataDxfId="66" totalsRowDxfId="0">
       <calculatedColumnFormula>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{B733589E-CC1B-4B28-A999-923AB100B27F}" name="Книги" totalsRowFunction="count" dataDxfId="34"/>
+    <tableColumn id="14" xr3:uid="{B733589E-CC1B-4B28-A999-923AB100B27F}" name="Книги" totalsRowFunction="count" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{74BBCFCF-F2D9-461C-A9CF-8B51B1D87C11}" name="Таблица3" displayName="Таблица3" ref="B2:B23" totalsRowShown="0" dataDxfId="98" tableBorderDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{74BBCFCF-F2D9-461C-A9CF-8B51B1D87C11}" name="Таблица3" displayName="Таблица3" ref="B2:B23" totalsRowShown="0" dataDxfId="64" tableBorderDxfId="63">
   <autoFilter ref="B2:B23" xr:uid="{74BBCFCF-F2D9-461C-A9CF-8B51B1D87C11}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{548C7D26-047D-46D9-AA4C-BA337573E0C4}" name="Имя" dataDxfId="96"/>
+    <tableColumn id="1" xr3:uid="{548C7D26-047D-46D9-AA4C-BA337573E0C4}" name="Имя" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Список" displayName="Список" ref="B4:T32" totalsRowCount="1" totalsRowBorderDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Список" displayName="Список" ref="B4:T32" totalsRowCount="1" totalsRowBorderDxfId="61">
   <autoFilter ref="B4:T31" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:P31">
-    <sortCondition ref="B4:B31"/>
-  </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" totalsRowLabel="ЛР1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Фамилия, имя"/>
@@ -2644,10 +2571,10 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Вар. ЛР" totalsRowFunction="custom">
       <totalsRowFormula>SUM(H32:N32)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="08.сен" totalsRowDxfId="94"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="22.сен" totalsRowFunction="countNums" totalsRowDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="08.сен" totalsRowDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="22.сен" totalsRowFunction="countNums" totalsRowDxfId="59"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="06.окт" totalsRowFunction="countNums"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="20.окт" totalsRowFunction="custom" totalsRowDxfId="92">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="20.окт" totalsRowFunction="custom" totalsRowDxfId="58">
       <totalsRowFormula>COUNTIF(Список[20.окт],1)</totalsRowFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="17.ноя" totalsRowFunction="custom">
@@ -2666,10 +2593,10 @@
       <calculatedColumnFormula>COUNTA(Список[[#This Row],[08.сен]:[22.дек]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="27.окт" totalsRowFunction="countNums"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Баллы1" totalsRowDxfId="91"/>
-    <tableColumn id="18" xr3:uid="{7200B40B-4F63-4AF1-802E-17C04B272670}" name="ДЗ" totalsRowFunction="countNums" totalsRowDxfId="90"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Баллы2" totalsRowDxfId="89"/>
-    <tableColumn id="19" xr3:uid="{C554BA58-7D4A-4C7C-BA59-256175785E3F}" name="Баллы3" dataDxfId="88" totalsRowDxfId="87">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Баллы1" totalsRowDxfId="57"/>
+    <tableColumn id="18" xr3:uid="{7200B40B-4F63-4AF1-802E-17C04B272670}" name="ДЗ" totalsRowFunction="countNums" totalsRowDxfId="56"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Баллы2" totalsRowDxfId="55"/>
+    <tableColumn id="19" xr3:uid="{C554BA58-7D4A-4C7C-BA59-256175785E3F}" name="Баллы3" dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>Список[[#This Row],[Баллы1]]+Список[[#This Row],[Баллы2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2974,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739B64B1-3B11-463E-B8B7-D6701A3690E4}">
-  <dimension ref="B1:AI41"/>
+  <dimension ref="B1:AI40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.5703125" customWidth="1"/>
@@ -2987,16 +2914,16 @@
     <col min="8" max="10" width="7.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="12" width="6.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="13" max="13" width="7" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="4.85546875" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="6.28515625" customWidth="1" collapsed="1"/>
     <col min="15" max="18" width="7.140625" customWidth="1"/>
-    <col min="19" max="19" width="7.85546875" customWidth="1"/>
+    <col min="19" max="19" width="12.42578125" customWidth="1"/>
     <col min="20" max="27" width="9.140625" hidden="1" customWidth="1" outlineLevel="2"/>
     <col min="28" max="28" width="6.42578125" customWidth="1" collapsed="1"/>
     <col min="29" max="29" width="7.140625" customWidth="1"/>
     <col min="30" max="30" width="7.5703125" customWidth="1"/>
     <col min="31" max="31" width="8" customWidth="1"/>
     <col min="32" max="32" width="7.42578125" customWidth="1"/>
-    <col min="33" max="33" width="8" customWidth="1"/>
+    <col min="33" max="33" width="11.85546875" customWidth="1"/>
     <col min="34" max="34" width="7.42578125" customWidth="1"/>
     <col min="35" max="35" width="47.5703125" customWidth="1"/>
   </cols>
@@ -3006,7 +2933,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="2:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:35" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G2" s="35" t="s">
         <v>164</v>
       </c>
@@ -3106,7 +3033,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:35" ht="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
@@ -3147,16 +3074,16 @@
       <c r="N5" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="O5" s="42" t="s">
+      <c r="O5" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="P5" s="43" t="s">
+      <c r="P5" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="Q5" s="43" t="s">
+      <c r="Q5" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="R5" s="43" t="s">
+      <c r="R5" s="39" t="s">
         <v>86</v>
       </c>
       <c r="S5" t="s">
@@ -3212,19 +3139,19 @@
       </c>
     </row>
     <row r="6" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B6" s="46">
-        <v>1</v>
-      </c>
-      <c r="C6" s="46" t="s">
+      <c r="B6" s="40">
+        <v>1</v>
+      </c>
+      <c r="C6" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="40">
         <v>1</v>
       </c>
       <c r="G6" s="34" t="s">
@@ -3236,21 +3163,21 @@
       <c r="I6" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46">
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O6" s="46">
+      <c r="O6" s="40">
         <v>4</v>
       </c>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46">
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>7</v>
       </c>
@@ -3266,96 +3193,96 @@
       <c r="Y6" s="34"/>
       <c r="Z6" s="34"/>
       <c r="AA6" s="34"/>
-      <c r="AB6" s="46">
+      <c r="AB6" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC6" s="46">
+      <c r="AC6" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD6" s="46">
+      <c r="AD6" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE6" s="46">
+      <c r="AE6" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF6" s="46">
+      <c r="AF6" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG6" s="46">
+      <c r="AG6" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>2</v>
       </c>
-      <c r="AH6" s="46">
+      <c r="AH6" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>9</v>
       </c>
-      <c r="AI6" s="44" t="s">
+      <c r="AI6" s="40" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="7" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B7" s="46">
+      <c r="B7" s="49">
         <v>2</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="46">
+      <c r="F7" s="49"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="49">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>0</v>
       </c>
-      <c r="O7" s="46"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="46">
+      <c r="O7" s="49"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="49">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>0</v>
       </c>
-      <c r="T7" s="34"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="47"/>
-      <c r="AA7" s="34"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="51"/>
+      <c r="AA7" s="50"/>
       <c r="AB7" s="49">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="46">
+      <c r="AC7" s="49">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD7" s="46">
+      <c r="AD7" s="49">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="46">
+      <c r="AE7" s="49">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="46">
+      <c r="AF7" s="49">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
@@ -3363,26 +3290,26 @@
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="46">
+      <c r="AH7" s="49">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="44"/>
+      <c r="AI7" s="40"/>
     </row>
     <row r="8" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B8" s="46">
+      <c r="B8" s="40">
         <v>3</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="46"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="34" t="s">
         <v>76</v>
       </c>
@@ -3391,20 +3318,20 @@
         <v>76</v>
       </c>
       <c r="J8" s="34"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46">
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O8" s="46">
+      <c r="O8" s="40">
         <v>7</v>
       </c>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46">
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>9</v>
       </c>
@@ -3418,137 +3345,137 @@
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
       <c r="AA8" s="34"/>
-      <c r="AB8" s="46">
+      <c r="AB8" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>1</v>
       </c>
-      <c r="AC8" s="46">
+      <c r="AC8" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD8" s="46">
+      <c r="AD8" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE8" s="46">
+      <c r="AE8" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="46">
+      <c r="AF8" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG8" s="46">
+      <c r="AG8" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>1</v>
       </c>
-      <c r="AH8" s="46">
+      <c r="AH8" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>10</v>
       </c>
-      <c r="AI8" s="44"/>
+      <c r="AI8" s="40"/>
     </row>
     <row r="9" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B9" s="46">
+      <c r="B9" s="40">
         <v>4</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="40">
         <v>4</v>
       </c>
       <c r="G9" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H9" s="47"/>
+      <c r="H9" s="42"/>
       <c r="I9" s="34" t="s">
         <v>76</v>
       </c>
       <c r="J9" s="34"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46">
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O9" s="46">
+      <c r="O9" s="40">
         <v>5</v>
       </c>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46">
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>7</v>
       </c>
       <c r="T9" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U9" s="47"/>
+      <c r="U9" s="42"/>
       <c r="V9" s="34"/>
       <c r="W9" s="34"/>
       <c r="X9" s="34"/>
       <c r="Y9" s="34"/>
       <c r="Z9" s="34"/>
       <c r="AA9" s="34"/>
-      <c r="AB9" s="46">
+      <c r="AB9" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>1</v>
       </c>
-      <c r="AC9" s="46">
+      <c r="AC9" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD9" s="46">
+      <c r="AD9" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="46">
+      <c r="AE9" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF9" s="46">
+      <c r="AF9" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG9" s="46">
+      <c r="AG9" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>1</v>
       </c>
-      <c r="AH9" s="46">
+      <c r="AH9" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>8</v>
       </c>
-      <c r="AI9" s="44"/>
+      <c r="AI9" s="40"/>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B10" s="46">
+      <c r="B10" s="40">
         <v>5</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="40">
         <v>5</v>
       </c>
       <c r="G10" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="47" t="s">
+      <c r="H10" s="42" t="s">
         <v>76</v>
       </c>
       <c r="I10" s="34" t="s">
@@ -3558,252 +3485,258 @@
       <c r="K10" s="34"/>
       <c r="L10" s="34"/>
       <c r="M10" s="34"/>
-      <c r="N10" s="46">
+      <c r="N10" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O10" s="46">
+      <c r="O10" s="40">
         <v>8</v>
       </c>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46">
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>11</v>
       </c>
       <c r="T10" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U10" s="47">
-        <v>1</v>
-      </c>
-      <c r="V10" s="34"/>
+      <c r="U10" s="42">
+        <v>1</v>
+      </c>
+      <c r="V10" s="34">
+        <v>2</v>
+      </c>
       <c r="W10" s="34"/>
       <c r="X10" s="34"/>
       <c r="Y10" s="34"/>
       <c r="Z10" s="34"/>
       <c r="AA10" s="34"/>
-      <c r="AB10" s="46">
+      <c r="AB10" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC10" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD10" s="46">
+      <c r="AD10" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="46">
+        <v>8</v>
+      </c>
+      <c r="AE10" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="46">
+      <c r="AF10" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="46">
+      <c r="AG10" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH10" s="46">
+        <v>19</v>
+      </c>
+      <c r="AH10" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>21</v>
-      </c>
-      <c r="AI10" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI10" s="40" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="11" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B11" s="46">
+      <c r="B11" s="40">
         <v>6</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="40">
         <v>6</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J11" s="46"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
+      <c r="H11" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="40"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
       <c r="M11" s="34"/>
-      <c r="N11" s="46">
+      <c r="N11" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O11" s="46">
+      <c r="O11" s="40">
         <v>10</v>
       </c>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46">
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
       <c r="T11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U11" s="47" t="s">
+      <c r="U11" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="V11" s="47"/>
+      <c r="V11" s="42">
+        <v>1</v>
+      </c>
       <c r="W11" s="34"/>
-      <c r="X11" s="47"/>
-      <c r="Y11" s="47"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="42"/>
       <c r="Z11" s="34"/>
       <c r="AA11" s="34"/>
-      <c r="AB11" s="46">
+      <c r="AB11" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC11" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC11" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE11" s="46">
+      <c r="AE11" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="46">
+      <c r="AF11" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG11" s="46">
+      <c r="AG11" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>2</v>
-      </c>
-      <c r="AH11" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH11" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>15</v>
-      </c>
-      <c r="AI11" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI11" s="40" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="12" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B12" s="46">
+      <c r="B12" s="40">
         <v>7</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="40">
         <v>7</v>
       </c>
       <c r="G12" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="47" t="s">
+      <c r="H12" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="42" t="s">
         <v>76</v>
       </c>
       <c r="J12" s="34"/>
       <c r="K12" s="34"/>
       <c r="L12" s="34"/>
       <c r="M12" s="34"/>
-      <c r="N12" s="46">
+      <c r="N12" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O12" s="46">
+      <c r="O12" s="40">
         <v>10</v>
       </c>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="46">
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
       <c r="T12" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U12" s="47" t="s">
+      <c r="U12" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="V12" s="47"/>
+      <c r="V12" s="42">
+        <v>1</v>
+      </c>
       <c r="W12" s="34"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="34"/>
       <c r="Z12" s="34"/>
       <c r="AA12" s="34"/>
-      <c r="AB12" s="46">
+      <c r="AB12" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC12" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD12" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="46">
+      <c r="AE12" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="46">
+      <c r="AF12" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG12" s="46">
+      <c r="AG12" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>2</v>
-      </c>
-      <c r="AH12" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH12" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>15</v>
-      </c>
-      <c r="AI12" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI12" s="40" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="13" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B13" s="46">
+      <c r="B13" s="40">
         <v>8</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="40">
         <v>7</v>
       </c>
       <c r="G13" s="34" t="s">
@@ -3819,17 +3752,17 @@
       <c r="K13" s="34"/>
       <c r="L13" s="34"/>
       <c r="M13" s="34"/>
-      <c r="N13" s="46">
+      <c r="N13" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O13" s="46">
+      <c r="O13" s="40">
         <v>8</v>
       </c>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46">
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>11</v>
       </c>
@@ -3839,56 +3772,58 @@
       <c r="U13" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="V13" s="34"/>
+      <c r="V13" s="34">
+        <v>1</v>
+      </c>
       <c r="W13" s="34"/>
       <c r="X13" s="34"/>
       <c r="Y13" s="34"/>
       <c r="Z13" s="34"/>
       <c r="AA13" s="34"/>
-      <c r="AB13" s="46">
+      <c r="AB13" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC13" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC13" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD13" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE13" s="46">
+      <c r="AE13" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="46">
+      <c r="AF13" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG13" s="46">
+      <c r="AG13" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>2</v>
-      </c>
-      <c r="AH13" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH13" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>13</v>
-      </c>
-      <c r="AI13" s="44"/>
+        <v>22</v>
+      </c>
+      <c r="AI13" s="40"/>
     </row>
     <row r="14" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B14" s="46">
+      <c r="B14" s="40">
         <v>9</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="43">
         <v>9</v>
       </c>
       <c r="G14" s="34" t="s">
@@ -3904,17 +3839,17 @@
       <c r="K14" s="34"/>
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
-      <c r="N14" s="46">
+      <c r="N14" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O14" s="46">
+      <c r="O14" s="40">
         <v>8</v>
       </c>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46">
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>11</v>
       </c>
@@ -3924,141 +3859,145 @@
       <c r="U14" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="V14" s="34"/>
+      <c r="V14" s="34">
+        <v>1</v>
+      </c>
       <c r="W14" s="34"/>
       <c r="X14" s="34"/>
       <c r="Y14" s="34"/>
       <c r="Z14" s="34"/>
       <c r="AA14" s="34"/>
-      <c r="AB14" s="46">
+      <c r="AB14" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC14" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="46">
+      <c r="AE14" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="46">
+      <c r="AF14" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="46">
+      <c r="AG14" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>2</v>
-      </c>
-      <c r="AH14" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH14" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>13</v>
-      </c>
-      <c r="AI14" s="44"/>
+        <v>22</v>
+      </c>
+      <c r="AI14" s="40"/>
     </row>
     <row r="15" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B15" s="46">
+      <c r="B15" s="40">
         <v>10</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="46">
+      <c r="F15" s="40">
         <v>3</v>
       </c>
       <c r="G15" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H15" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="46"/>
+      <c r="H15" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="40"/>
       <c r="K15" s="34"/>
       <c r="L15" s="34"/>
       <c r="M15" s="34"/>
-      <c r="N15" s="46">
+      <c r="N15" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O15" s="46">
+      <c r="O15" s="40">
         <v>10</v>
       </c>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46">
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
       <c r="T15" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U15" s="47">
-        <v>1</v>
-      </c>
-      <c r="V15" s="47"/>
+      <c r="U15" s="42">
+        <v>1</v>
+      </c>
+      <c r="V15" s="42">
+        <v>2</v>
+      </c>
       <c r="W15" s="34"/>
       <c r="X15" s="34"/>
       <c r="Y15" s="34"/>
       <c r="Z15" s="34"/>
       <c r="AA15" s="34"/>
-      <c r="AB15" s="46">
+      <c r="AB15" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC15" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC15" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD15" s="46">
+      <c r="AD15" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="46">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="46">
+      <c r="AF15" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="46">
+      <c r="AG15" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH15" s="46">
+        <v>19</v>
+      </c>
+      <c r="AH15" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>23</v>
-      </c>
-      <c r="AI15" s="44"/>
+        <v>32</v>
+      </c>
+      <c r="AI15" s="40"/>
     </row>
     <row r="16" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B16" s="46">
+      <c r="B16" s="40">
         <v>11</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="40">
         <v>5</v>
       </c>
       <c r="G16" s="34" t="s">
@@ -4072,17 +4011,17 @@
       <c r="K16" s="34"/>
       <c r="L16" s="34"/>
       <c r="M16" s="34"/>
-      <c r="N16" s="46">
+      <c r="N16" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O16" s="46">
+      <c r="O16" s="40">
         <v>10</v>
       </c>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46">
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>12</v>
       </c>
@@ -4096,50 +4035,50 @@
       <c r="Y16" s="34"/>
       <c r="Z16" s="34"/>
       <c r="AA16" s="34"/>
-      <c r="AB16" s="46">
+      <c r="AB16" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>1</v>
       </c>
-      <c r="AC16" s="46">
+      <c r="AC16" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD16" s="46">
+      <c r="AD16" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE16" s="46">
+      <c r="AE16" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="46">
+      <c r="AF16" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG16" s="46">
+      <c r="AG16" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>1</v>
       </c>
-      <c r="AH16" s="46">
+      <c r="AH16" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>13</v>
       </c>
-      <c r="AI16" s="44"/>
+      <c r="AI16" s="40"/>
     </row>
     <row r="17" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B17" s="46">
+      <c r="B17" s="40">
         <v>12</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="46" t="s">
+      <c r="E17" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="40">
         <v>12</v>
       </c>
       <c r="G17" s="34" t="s">
@@ -4155,17 +4094,17 @@
       <c r="K17" s="34"/>
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
-      <c r="N17" s="46">
+      <c r="N17" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O17" s="46">
+      <c r="O17" s="40">
         <v>10</v>
       </c>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46">
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
@@ -4175,58 +4114,60 @@
       <c r="U17" s="34">
         <v>1</v>
       </c>
-      <c r="V17" s="34"/>
+      <c r="V17" s="34">
+        <v>2</v>
+      </c>
       <c r="W17" s="34"/>
       <c r="X17" s="34"/>
       <c r="Y17" s="34"/>
       <c r="Z17" s="34"/>
       <c r="AA17" s="34"/>
-      <c r="AB17" s="46">
+      <c r="AB17" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC17" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD17" s="46">
+      <c r="AD17" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="46">
+        <v>8</v>
+      </c>
+      <c r="AE17" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF17" s="46">
+      <c r="AF17" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG17" s="46">
+      <c r="AG17" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH17" s="46">
+        <v>19</v>
+      </c>
+      <c r="AH17" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>23</v>
-      </c>
-      <c r="AI17" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI17" s="44" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="18" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B18" s="46">
+      <c r="B18" s="40">
         <v>13</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="E18" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="40">
         <v>13</v>
       </c>
       <c r="G18" s="34" t="s">
@@ -4240,19 +4181,19 @@
       </c>
       <c r="J18" s="34"/>
       <c r="K18" s="34"/>
-      <c r="L18" s="47"/>
+      <c r="L18" s="42"/>
       <c r="M18" s="34"/>
-      <c r="N18" s="46">
+      <c r="N18" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O18" s="46">
+      <c r="O18" s="40">
         <v>10</v>
       </c>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="46"/>
-      <c r="S18" s="46">
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
@@ -4265,55 +4206,55 @@
       <c r="V18" s="34"/>
       <c r="W18" s="34"/>
       <c r="X18" s="34"/>
-      <c r="Y18" s="47"/>
+      <c r="Y18" s="42"/>
       <c r="Z18" s="34"/>
       <c r="AA18" s="34"/>
-      <c r="AB18" s="46">
+      <c r="AB18" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC18" s="46">
+      <c r="AC18" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD18" s="46">
+      <c r="AD18" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE18" s="46">
+      <c r="AE18" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF18" s="46">
+      <c r="AF18" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG18" s="46">
+      <c r="AG18" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>10</v>
       </c>
-      <c r="AH18" s="46">
+      <c r="AH18" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>23</v>
       </c>
-      <c r="AI18" s="51" t="s">
+      <c r="AI18" s="44" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="19" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B19" s="46">
+      <c r="B19" s="40">
         <v>14</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="E19" s="46" t="s">
+      <c r="E19" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="46">
+      <c r="F19" s="40">
         <v>14</v>
       </c>
       <c r="G19" s="34" t="s">
@@ -4325,19 +4266,19 @@
       </c>
       <c r="J19" s="34"/>
       <c r="K19" s="34"/>
-      <c r="L19" s="47"/>
+      <c r="L19" s="42"/>
       <c r="M19" s="34"/>
-      <c r="N19" s="46">
+      <c r="N19" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O19" s="46">
+      <c r="O19" s="40">
         <v>10</v>
       </c>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46">
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>12</v>
       </c>
@@ -4347,58 +4288,60 @@
       <c r="U19" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="V19" s="34"/>
+      <c r="V19" s="34">
+        <v>1</v>
+      </c>
       <c r="W19" s="34"/>
       <c r="X19" s="34"/>
-      <c r="Y19" s="47"/>
+      <c r="Y19" s="42"/>
       <c r="Z19" s="34"/>
       <c r="AA19" s="34"/>
-      <c r="AB19" s="46">
+      <c r="AB19" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC19" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC19" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD19" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE19" s="46">
+      <c r="AE19" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="46">
+      <c r="AF19" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG19" s="46">
+      <c r="AG19" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>2</v>
-      </c>
-      <c r="AH19" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH19" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>14</v>
-      </c>
-      <c r="AI19" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI19" s="40" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B20" s="46">
+      <c r="B20" s="40">
         <v>15</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="46" t="s">
+      <c r="E20" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="46">
+      <c r="F20" s="40">
         <v>15</v>
       </c>
       <c r="G20" s="34" t="s">
@@ -4410,19 +4353,19 @@
       </c>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
-      <c r="L20" s="47"/>
+      <c r="L20" s="42"/>
       <c r="M20" s="34"/>
-      <c r="N20" s="46">
+      <c r="N20" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O20" s="46">
+      <c r="O20" s="40">
         <v>10</v>
       </c>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46">
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>12</v>
       </c>
@@ -4432,62 +4375,64 @@
       <c r="U20" s="34">
         <v>1</v>
       </c>
-      <c r="V20" s="34"/>
+      <c r="V20" s="34" t="s">
+        <v>76</v>
+      </c>
       <c r="W20" s="34"/>
       <c r="X20" s="34"/>
-      <c r="Y20" s="47"/>
+      <c r="Y20" s="42"/>
       <c r="Z20" s="34"/>
       <c r="AA20" s="34"/>
-      <c r="AB20" s="46">
+      <c r="AB20" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC20" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD20" s="46">
+      <c r="AD20" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE20" s="46">
+      <c r="AE20" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="46">
+      <c r="AF20" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG20" s="46">
+      <c r="AG20" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH20" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH20" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>22</v>
-      </c>
-      <c r="AI20" s="44"/>
+        <v>23</v>
+      </c>
+      <c r="AI20" s="40"/>
     </row>
     <row r="21" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B21" s="46">
+      <c r="B21" s="40">
         <v>16</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="46" t="s">
+      <c r="E21" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="46">
+      <c r="F21" s="40">
         <v>13</v>
       </c>
       <c r="G21" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="47"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="34" t="s">
         <v>76</v>
       </c>
@@ -4495,24 +4440,24 @@
       <c r="K21" s="34"/>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
-      <c r="N21" s="46">
+      <c r="N21" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O21" s="46">
+      <c r="O21" s="40">
         <v>10</v>
       </c>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46">
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>12</v>
       </c>
       <c r="T21" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U21" s="47">
+      <c r="U21" s="42">
         <v>1</v>
       </c>
       <c r="V21" s="34"/>
@@ -4521,303 +4466,307 @@
       <c r="Y21" s="34"/>
       <c r="Z21" s="34"/>
       <c r="AA21" s="34"/>
-      <c r="AB21" s="46">
+      <c r="AB21" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC21" s="46">
+      <c r="AC21" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD21" s="46">
+      <c r="AD21" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE21" s="46">
+      <c r="AE21" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF21" s="46">
+      <c r="AF21" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG21" s="46">
+      <c r="AG21" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>10</v>
       </c>
-      <c r="AH21" s="46">
+      <c r="AH21" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>22</v>
       </c>
-      <c r="AI21" s="44"/>
+      <c r="AI21" s="40"/>
     </row>
     <row r="22" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B22" s="46">
+      <c r="B22" s="40">
         <v>17</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="E22" s="46" t="s">
+      <c r="E22" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="40">
         <v>15</v>
       </c>
       <c r="G22" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22" s="46"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="40"/>
       <c r="K22" s="34"/>
-      <c r="L22" s="47"/>
+      <c r="L22" s="42"/>
       <c r="M22" s="34"/>
-      <c r="N22" s="46">
+      <c r="N22" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O22" s="46">
+      <c r="O22" s="40">
         <v>9</v>
       </c>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46">
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>11</v>
       </c>
       <c r="T22" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U22" s="47">
-        <v>1</v>
-      </c>
-      <c r="V22" s="47"/>
+      <c r="U22" s="42">
+        <v>1</v>
+      </c>
+      <c r="V22" s="42" t="s">
+        <v>76</v>
+      </c>
       <c r="W22" s="34"/>
       <c r="X22" s="34"/>
-      <c r="Y22" s="47"/>
+      <c r="Y22" s="42"/>
       <c r="Z22" s="34"/>
       <c r="AA22" s="34"/>
-      <c r="AB22" s="46">
+      <c r="AB22" s="40">
+        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
+        <v>3</v>
+      </c>
+      <c r="AC22" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
+        <v>8</v>
+      </c>
+      <c r="AD22" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="40">
+        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
+        <v>11</v>
+      </c>
+      <c r="AH22" s="40">
+        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
+        <v>22</v>
+      </c>
+      <c r="AI22" s="40"/>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B23" s="40">
+        <v>18</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="40">
+        <v>18</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" s="40"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="40">
+        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
+        <v>3</v>
+      </c>
+      <c r="O23" s="40">
+        <v>9</v>
+      </c>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40">
+        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
+        <v>12</v>
+      </c>
+      <c r="T23" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="U23" s="42">
+        <v>1</v>
+      </c>
+      <c r="V23" s="42"/>
+      <c r="W23" s="34"/>
+      <c r="X23" s="34"/>
+      <c r="Y23" s="42"/>
+      <c r="Z23" s="34"/>
+      <c r="AA23" s="34"/>
+      <c r="AB23" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC22" s="46">
+      <c r="AC23" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD22" s="46">
+      <c r="AD23" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE22" s="46">
+      <c r="AE23" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF22" s="46">
+      <c r="AF23" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="46">
+      <c r="AG23" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>10</v>
       </c>
-      <c r="AH22" s="46">
+      <c r="AH23" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>21</v>
-      </c>
-      <c r="AI22" s="44"/>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B23" s="46">
-        <v>18</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI23" s="40"/>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B24" s="40">
+        <v>19</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="46">
-        <v>18</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J23" s="46"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="46">
+      <c r="F24" s="40">
+        <v>19</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="40"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O23" s="46">
-        <v>9</v>
-      </c>
-      <c r="P23" s="46"/>
-      <c r="Q23" s="46"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="46">
+      <c r="O24" s="40">
+        <v>10</v>
+      </c>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
-        <v>12</v>
-      </c>
-      <c r="T23" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="U23" s="47">
-        <v>1</v>
-      </c>
-      <c r="V23" s="47"/>
-      <c r="W23" s="34"/>
-      <c r="X23" s="34"/>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="34"/>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="46">
+        <v>13</v>
+      </c>
+      <c r="T24" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="U24" s="42">
+        <v>1</v>
+      </c>
+      <c r="V24" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="W24" s="34"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="42"/>
+      <c r="Z24" s="34"/>
+      <c r="AA24" s="34"/>
+      <c r="AB24" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC23" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD23" s="46">
+      <c r="AD24" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE23" s="46">
+      <c r="AE24" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF23" s="46">
+      <c r="AF24" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG23" s="46">
+      <c r="AG24" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH23" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH24" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>22</v>
-      </c>
-      <c r="AI23" s="44"/>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B24" s="46">
-        <v>19</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="46">
-        <v>19</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J24" s="46"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="46">
-        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
-        <v>3</v>
-      </c>
-      <c r="O24" s="46">
-        <v>10</v>
-      </c>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46">
-        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
-        <v>13</v>
-      </c>
-      <c r="T24" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="U24" s="47">
-        <v>1</v>
-      </c>
-      <c r="V24" s="47"/>
-      <c r="W24" s="34"/>
-      <c r="X24" s="34"/>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="34"/>
-      <c r="AA24" s="34"/>
-      <c r="AB24" s="46">
-        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC24" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>8</v>
-      </c>
-      <c r="AD24" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="46">
-        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH24" s="46">
-        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>23</v>
-      </c>
-      <c r="AI24" s="44"/>
+        <v>24</v>
+      </c>
+      <c r="AI24" s="40"/>
     </row>
     <row r="25" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B25" s="46">
+      <c r="B25" s="40">
         <v>20</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="40">
         <v>16</v>
       </c>
       <c r="G25" s="34" t="s">
@@ -4829,19 +4778,19 @@
       </c>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
-      <c r="L25" s="47"/>
+      <c r="L25" s="42"/>
       <c r="M25" s="34"/>
-      <c r="N25" s="46">
+      <c r="N25" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O25" s="46">
+      <c r="O25" s="40">
         <v>10</v>
       </c>
-      <c r="P25" s="46"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46"/>
-      <c r="S25" s="46">
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>12</v>
       </c>
@@ -4854,77 +4803,77 @@
       <c r="V25" s="34"/>
       <c r="W25" s="34"/>
       <c r="X25" s="34"/>
-      <c r="Y25" s="47"/>
+      <c r="Y25" s="42"/>
       <c r="Z25" s="34"/>
       <c r="AA25" s="34"/>
-      <c r="AB25" s="46">
+      <c r="AB25" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC25" s="46">
+      <c r="AC25" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD25" s="46">
+      <c r="AD25" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="46">
+      <c r="AE25" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF25" s="46">
+      <c r="AF25" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="46">
+      <c r="AG25" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>2</v>
       </c>
-      <c r="AH25" s="46">
+      <c r="AH25" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>14</v>
       </c>
-      <c r="AI25" s="44"/>
+      <c r="AI25" s="40"/>
     </row>
     <row r="26" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B26" s="46">
+      <c r="B26" s="40">
         <v>21</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D26" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="46">
+      <c r="F26" s="40">
         <v>14</v>
       </c>
       <c r="G26" s="34" t="s">
         <v>76</v>
       </c>
       <c r="H26" s="34"/>
-      <c r="I26" s="47" t="s">
+      <c r="I26" s="42" t="s">
         <v>76</v>
       </c>
       <c r="J26" s="34"/>
       <c r="K26" s="34"/>
       <c r="L26" s="34"/>
       <c r="M26" s="34"/>
-      <c r="N26" s="46">
+      <c r="N26" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O26" s="46">
+      <c r="O26" s="40">
         <v>10</v>
       </c>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46">
+      <c r="P26" s="40"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>12</v>
       </c>
@@ -4932,64 +4881,64 @@
         <v>76</v>
       </c>
       <c r="U26" s="34"/>
-      <c r="V26" s="47"/>
+      <c r="V26" s="42"/>
       <c r="W26" s="34"/>
       <c r="X26" s="34"/>
       <c r="Y26" s="34"/>
       <c r="Z26" s="34"/>
       <c r="AA26" s="34"/>
-      <c r="AB26" s="46">
+      <c r="AB26" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>1</v>
       </c>
-      <c r="AC26" s="46">
+      <c r="AC26" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD26" s="46">
+      <c r="AD26" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE26" s="46">
+      <c r="AE26" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF26" s="46">
+      <c r="AF26" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG26" s="46">
+      <c r="AG26" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>1</v>
       </c>
-      <c r="AH26" s="46">
+      <c r="AH26" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>13</v>
       </c>
-      <c r="AI26" s="51" t="s">
+      <c r="AI26" s="44" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="27" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B27" s="46">
+      <c r="B27" s="40">
         <v>22</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="E27" s="46" t="s">
+      <c r="E27" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="46">
+      <c r="F27" s="40">
         <v>3</v>
       </c>
       <c r="G27" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H27" s="47" t="s">
+      <c r="H27" s="42" t="s">
         <v>76</v>
       </c>
       <c r="I27" s="34" t="s">
@@ -4999,76 +4948,78 @@
       <c r="K27" s="34"/>
       <c r="L27" s="34"/>
       <c r="M27" s="34"/>
-      <c r="N27" s="46">
+      <c r="N27" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O27" s="46">
+      <c r="O27" s="40">
         <v>10</v>
       </c>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46">
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
       <c r="T27" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="U27" s="47">
-        <v>1</v>
-      </c>
-      <c r="V27" s="34"/>
+      <c r="U27" s="42">
+        <v>1</v>
+      </c>
+      <c r="V27" s="34" t="s">
+        <v>76</v>
+      </c>
       <c r="W27" s="34"/>
       <c r="X27" s="34"/>
       <c r="Y27" s="34"/>
       <c r="Z27" s="34"/>
       <c r="AA27" s="34"/>
-      <c r="AB27" s="46">
+      <c r="AB27" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC27" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD27" s="46">
+      <c r="AD27" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE27" s="46">
+      <c r="AE27" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF27" s="46">
+      <c r="AF27" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG27" s="46">
+      <c r="AG27" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH27" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH27" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
+        <v>24</v>
+      </c>
+      <c r="AI27" s="40"/>
+    </row>
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B28" s="40">
         <v>23</v>
       </c>
-      <c r="AI27" s="44"/>
-    </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B28" s="46">
-        <v>23</v>
-      </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="46" t="s">
+      <c r="E28" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="46">
+      <c r="F28" s="40">
         <v>16</v>
       </c>
       <c r="G28" s="34" t="s">
@@ -5077,24 +5028,24 @@
       <c r="H28" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I28" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J28" s="46"/>
+      <c r="I28" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" s="40"/>
       <c r="K28" s="34"/>
       <c r="L28" s="34"/>
       <c r="M28" s="34"/>
-      <c r="N28" s="46">
+      <c r="N28" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O28" s="46">
+      <c r="O28" s="40">
         <v>10</v>
       </c>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46">
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="40"/>
+      <c r="S28" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
@@ -5104,82 +5055,82 @@
       <c r="U28" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="V28" s="47"/>
+      <c r="V28" s="42"/>
       <c r="W28" s="34"/>
       <c r="X28" s="34"/>
       <c r="Y28" s="34"/>
       <c r="Z28" s="34"/>
       <c r="AA28" s="34"/>
-      <c r="AB28" s="46">
+      <c r="AB28" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC28" s="46">
+      <c r="AC28" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>0</v>
       </c>
-      <c r="AD28" s="46">
+      <c r="AD28" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE28" s="46">
+      <c r="AE28" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF28" s="46">
+      <c r="AF28" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="46">
+      <c r="AG28" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>2</v>
       </c>
-      <c r="AH28" s="46">
+      <c r="AH28" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>15</v>
       </c>
-      <c r="AI28" s="51" t="s">
+      <c r="AI28" s="44" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="29" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B29" s="46">
+      <c r="B29" s="40">
         <v>24</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="46" t="s">
+      <c r="E29" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="46">
+      <c r="F29" s="40">
         <v>21</v>
       </c>
       <c r="G29" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="46"/>
-      <c r="I29" s="47" t="s">
+      <c r="H29" s="40"/>
+      <c r="I29" s="42" t="s">
         <v>76</v>
       </c>
       <c r="J29" s="34"/>
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
       <c r="M29" s="34"/>
-      <c r="N29" s="46">
+      <c r="N29" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O29" s="46">
+      <c r="O29" s="40">
         <v>10</v>
       </c>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="46"/>
-      <c r="S29" s="46">
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>12</v>
       </c>
@@ -5187,56 +5138,58 @@
         <v>76</v>
       </c>
       <c r="U29" s="34"/>
-      <c r="V29" s="47"/>
+      <c r="V29" s="42">
+        <v>1</v>
+      </c>
       <c r="W29" s="34"/>
       <c r="X29" s="34"/>
       <c r="Y29" s="34"/>
       <c r="Z29" s="34"/>
       <c r="AA29" s="34"/>
-      <c r="AB29" s="46">
+      <c r="AB29" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>1</v>
-      </c>
-      <c r="AC29" s="46">
+        <v>2</v>
+      </c>
+      <c r="AC29" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD29" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE29" s="46">
+      <c r="AE29" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF29" s="46">
+      <c r="AF29" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG29" s="46">
+      <c r="AG29" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>1</v>
-      </c>
-      <c r="AH29" s="46">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>13</v>
-      </c>
-      <c r="AI29" s="44"/>
+        <v>22</v>
+      </c>
+      <c r="AI29" s="40"/>
     </row>
     <row r="30" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B30" s="46">
+      <c r="B30" s="40">
         <v>25</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="46" t="s">
+      <c r="D30" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="46" t="s">
+      <c r="E30" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="46">
+      <c r="F30" s="40">
         <v>6</v>
       </c>
       <c r="G30" s="34" t="s">
@@ -5245,24 +5198,24 @@
       <c r="H30" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I30" s="47" t="s">
+      <c r="I30" s="42" t="s">
         <v>76</v>
       </c>
       <c r="J30" s="34"/>
       <c r="K30" s="34"/>
-      <c r="L30" s="47"/>
+      <c r="L30" s="42"/>
       <c r="M30" s="34"/>
-      <c r="N30" s="46">
+      <c r="N30" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O30" s="46">
+      <c r="O30" s="40">
         <v>10</v>
       </c>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46">
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="40"/>
+      <c r="S30" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
@@ -5272,82 +5225,84 @@
       <c r="U30" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="V30" s="34"/>
+      <c r="V30" s="34">
+        <v>1</v>
+      </c>
       <c r="W30" s="34"/>
       <c r="X30" s="34"/>
-      <c r="Y30" s="47"/>
+      <c r="Y30" s="42"/>
       <c r="Z30" s="34"/>
       <c r="AA30" s="34"/>
-      <c r="AB30" s="46">
+      <c r="AB30" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC30" s="46">
+        <v>3</v>
+      </c>
+      <c r="AC30" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD30" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE30" s="46">
+      <c r="AE30" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF30" s="46">
+      <c r="AF30" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG30" s="46">
+      <c r="AG30" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>2</v>
-      </c>
-      <c r="AH30" s="46">
+        <v>11</v>
+      </c>
+      <c r="AH30" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>15</v>
-      </c>
-      <c r="AI30" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI30" s="40" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="31" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B31" s="46">
+      <c r="B31" s="40">
         <v>26</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="46" t="s">
+      <c r="D31" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="46">
+      <c r="F31" s="40">
         <v>9</v>
       </c>
       <c r="G31" s="34" t="s">
         <v>76</v>
       </c>
       <c r="H31" s="34"/>
-      <c r="I31" s="47" t="s">
+      <c r="I31" s="42" t="s">
         <v>76</v>
       </c>
       <c r="J31" s="34"/>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
       <c r="M31" s="34"/>
-      <c r="N31" s="46">
+      <c r="N31" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>2</v>
       </c>
-      <c r="O31" s="46">
+      <c r="O31" s="40">
         <v>9</v>
       </c>
-      <c r="P31" s="46"/>
-      <c r="Q31" s="46"/>
-      <c r="R31" s="46"/>
-      <c r="S31" s="46">
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="40"/>
+      <c r="S31" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>11</v>
       </c>
@@ -5355,84 +5310,86 @@
         <v>76</v>
       </c>
       <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
+      <c r="V31" s="34">
+        <v>1</v>
+      </c>
       <c r="W31" s="34"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="34"/>
       <c r="Z31" s="34"/>
       <c r="AA31" s="34"/>
-      <c r="AB31" s="46">
+      <c r="AB31" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>1</v>
-      </c>
-      <c r="AC31" s="46">
+        <v>2</v>
+      </c>
+      <c r="AC31" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="46">
+        <v>8</v>
+      </c>
+      <c r="AD31" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE31" s="46">
+      <c r="AE31" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF31" s="46">
+      <c r="AF31" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG31" s="46">
+      <c r="AG31" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>1</v>
-      </c>
-      <c r="AH31" s="46">
+        <v>10</v>
+      </c>
+      <c r="AH31" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
+        <v>21</v>
+      </c>
+      <c r="AI31" s="44" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="40">
+        <v>27</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="40">
         <v>12</v>
       </c>
-      <c r="AI31" s="51" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="32" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="46">
-        <v>27</v>
-      </c>
-      <c r="C32" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F32" s="46">
-        <v>12</v>
-      </c>
       <c r="G32" s="34" t="s">
         <v>76</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I32" s="47" t="s">
+      <c r="I32" s="42" t="s">
         <v>76</v>
       </c>
       <c r="J32" s="34"/>
       <c r="K32" s="34"/>
       <c r="L32" s="34"/>
       <c r="M32" s="34"/>
-      <c r="N32" s="46">
+      <c r="N32" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O32" s="46">
+      <c r="O32" s="40">
         <v>10</v>
       </c>
-      <c r="P32" s="46"/>
-      <c r="Q32" s="46"/>
-      <c r="R32" s="46"/>
-      <c r="S32" s="46">
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="40"/>
+      <c r="S32" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
@@ -5442,469 +5399,477 @@
       <c r="U32" s="34">
         <v>1</v>
       </c>
-      <c r="V32" s="34"/>
+      <c r="V32" s="34">
+        <v>2</v>
+      </c>
       <c r="W32" s="34"/>
       <c r="X32" s="34"/>
       <c r="Y32" s="34"/>
       <c r="Z32" s="34"/>
       <c r="AA32" s="34"/>
-      <c r="AB32" s="46">
+      <c r="AB32" s="40">
+        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
+        <v>3</v>
+      </c>
+      <c r="AC32" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
+        <v>8</v>
+      </c>
+      <c r="AD32" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
+        <v>8</v>
+      </c>
+      <c r="AE32" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF32" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
+        <v>0</v>
+      </c>
+      <c r="AG32" s="40">
+        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
+        <v>19</v>
+      </c>
+      <c r="AH32" s="40">
+        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
+        <v>32</v>
+      </c>
+      <c r="AI32" s="40" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B33" s="40">
+        <v>28</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="40">
+        <v>1</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J33" s="42"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="40">
+        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
+        <v>3</v>
+      </c>
+      <c r="O33" s="40">
+        <v>9</v>
+      </c>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="40"/>
+      <c r="S33" s="40">
+        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
+        <v>12</v>
+      </c>
+      <c r="T33" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="U33" s="42"/>
+      <c r="V33" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="W33" s="42"/>
+      <c r="X33" s="34"/>
+      <c r="Y33" s="42"/>
+      <c r="Z33" s="34"/>
+      <c r="AA33" s="34"/>
+      <c r="AB33" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC32" s="46">
+      <c r="AC33" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
+        <v>0</v>
+      </c>
+      <c r="AD33" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
+        <v>0</v>
+      </c>
+      <c r="AE33" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF33" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
+        <v>0</v>
+      </c>
+      <c r="AG33" s="40">
+        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
+        <v>2</v>
+      </c>
+      <c r="AH33" s="40">
+        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
+        <v>14</v>
+      </c>
+      <c r="AI33" s="40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B34" s="40">
+        <v>29</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" s="40">
+        <v>4</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34" s="42"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="40">
+        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
+        <v>2</v>
+      </c>
+      <c r="O34" s="40">
+        <v>9</v>
+      </c>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="40"/>
+      <c r="S34" s="40">
+        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
+        <v>11</v>
+      </c>
+      <c r="T34" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="U34" s="42"/>
+      <c r="V34" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="W34" s="42"/>
+      <c r="X34" s="34"/>
+      <c r="Y34" s="42"/>
+      <c r="Z34" s="34"/>
+      <c r="AA34" s="34"/>
+      <c r="AB34" s="40">
+        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
+        <v>2</v>
+      </c>
+      <c r="AC34" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
+        <v>0</v>
+      </c>
+      <c r="AD34" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
+        <v>0</v>
+      </c>
+      <c r="AE34" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF34" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
+        <v>0</v>
+      </c>
+      <c r="AG34" s="40">
+        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
+        <v>2</v>
+      </c>
+      <c r="AH34" s="40">
+        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
+        <v>13</v>
+      </c>
+      <c r="AI34" s="40"/>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B35" s="40">
+        <v>30</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="40">
+        <v>18</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J35" s="42"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="40">
+        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
+        <v>3</v>
+      </c>
+      <c r="O35" s="40">
+        <v>10</v>
+      </c>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="40"/>
+      <c r="S35" s="40">
+        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
+        <v>13</v>
+      </c>
+      <c r="T35" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="U35" s="42">
+        <v>1</v>
+      </c>
+      <c r="V35" s="34"/>
+      <c r="W35" s="42"/>
+      <c r="X35" s="34"/>
+      <c r="Y35" s="42"/>
+      <c r="Z35" s="34"/>
+      <c r="AA35" s="34"/>
+      <c r="AB35" s="40">
+        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
+        <v>2</v>
+      </c>
+      <c r="AC35" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD32" s="46">
+      <c r="AD35" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE32" s="46">
+      <c r="AE35" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF32" s="46">
+      <c r="AF35" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG32" s="46">
+      <c r="AG35" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>10</v>
       </c>
-      <c r="AH32" s="46">
+      <c r="AH35" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>23</v>
       </c>
-      <c r="AI32" s="44" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B33" s="46">
+      <c r="AI35" s="40"/>
+    </row>
+    <row r="36" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B36" s="40">
+        <v>31</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="40">
+        <v>21</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="40">
+        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
+        <v>2</v>
+      </c>
+      <c r="O36" s="40">
+        <v>10</v>
+      </c>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="40"/>
+      <c r="S36" s="40">
+        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
+        <v>12</v>
+      </c>
+      <c r="T36" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="U36" s="42"/>
+      <c r="V36" s="34">
+        <v>1</v>
+      </c>
+      <c r="W36" s="42"/>
+      <c r="X36" s="34"/>
+      <c r="Y36" s="42"/>
+      <c r="Z36" s="34"/>
+      <c r="AA36" s="34"/>
+      <c r="AB36" s="40">
+        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
+        <v>2</v>
+      </c>
+      <c r="AC36" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
+        <v>8</v>
+      </c>
+      <c r="AD36" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
+        <v>0</v>
+      </c>
+      <c r="AE36" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
+        <v>0</v>
+      </c>
+      <c r="AF36" s="40">
+        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
+        <v>0</v>
+      </c>
+      <c r="AG36" s="40">
+        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
+        <v>10</v>
+      </c>
+      <c r="AH36" s="40">
+        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
+        <v>22</v>
+      </c>
+      <c r="AI36" s="40"/>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B37" s="40">
+        <v>32</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="46">
-        <v>1</v>
-      </c>
-      <c r="G33" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H33" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I33" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J33" s="47"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="46">
+      <c r="F37" s="40">
+        <v>19</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="J37" s="42"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="40">
         <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
         <v>3</v>
       </c>
-      <c r="O33" s="46">
-        <v>9</v>
-      </c>
-      <c r="P33" s="46"/>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="46"/>
-      <c r="S33" s="46">
-        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
-        <v>12</v>
-      </c>
-      <c r="T33" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="U33" s="47"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="47"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="47"/>
-      <c r="Z33" s="34"/>
-      <c r="AA33" s="34"/>
-      <c r="AB33" s="46">
-        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>1</v>
-      </c>
-      <c r="AC33" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD33" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE33" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
-        <v>0</v>
-      </c>
-      <c r="AF33" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="46">
-        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>1</v>
-      </c>
-      <c r="AH33" s="46">
-        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>13</v>
-      </c>
-      <c r="AI33" s="44" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B34" s="46">
-        <v>29</v>
-      </c>
-      <c r="C34" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="46">
-        <v>4</v>
-      </c>
-      <c r="G34" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J34" s="47"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="46">
-        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="O34" s="46">
-        <v>9</v>
-      </c>
-      <c r="P34" s="46"/>
-      <c r="Q34" s="46"/>
-      <c r="R34" s="46"/>
-      <c r="S34" s="46">
-        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
-        <v>11</v>
-      </c>
-      <c r="T34" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="U34" s="47"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="34"/>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="46">
-        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>1</v>
-      </c>
-      <c r="AC34" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD34" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE34" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
-        <v>0</v>
-      </c>
-      <c r="AF34" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
-        <v>0</v>
-      </c>
-      <c r="AG34" s="46">
-        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>1</v>
-      </c>
-      <c r="AH34" s="46">
-        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>12</v>
-      </c>
-      <c r="AI34" s="44"/>
-    </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B35" s="46">
-        <v>30</v>
-      </c>
-      <c r="C35" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="46">
-        <v>18</v>
-      </c>
-      <c r="G35" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H35" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I35" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J35" s="47"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="46">
-        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
-        <v>3</v>
-      </c>
-      <c r="O35" s="46">
+      <c r="O37" s="40">
         <v>10</v>
       </c>
-      <c r="P35" s="46"/>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46">
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="40"/>
+      <c r="S37" s="40">
         <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
         <v>13</v>
       </c>
-      <c r="T35" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="U35" s="47">
-        <v>1</v>
-      </c>
-      <c r="V35" s="34"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="34"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="34"/>
-      <c r="AA35" s="34"/>
-      <c r="AB35" s="46">
+      <c r="T37" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="U37" s="42">
+        <v>1</v>
+      </c>
+      <c r="V37" s="34"/>
+      <c r="W37" s="42"/>
+      <c r="X37" s="34"/>
+      <c r="Y37" s="42"/>
+      <c r="Z37" s="34"/>
+      <c r="AA37" s="34"/>
+      <c r="AB37" s="40">
         <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
         <v>2</v>
       </c>
-      <c r="AC35" s="46">
+      <c r="AC37" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
         <v>8</v>
       </c>
-      <c r="AD35" s="46">
+      <c r="AD37" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
         <v>0</v>
       </c>
-      <c r="AE35" s="46">
+      <c r="AE37" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
         <v>0</v>
       </c>
-      <c r="AF35" s="46">
+      <c r="AF37" s="40">
         <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
         <v>0</v>
       </c>
-      <c r="AG35" s="46">
+      <c r="AG37" s="40">
         <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
         <v>10</v>
       </c>
-      <c r="AH35" s="46">
+      <c r="AH37" s="40">
         <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
         <v>23</v>
       </c>
-      <c r="AI35" s="44"/>
-    </row>
-    <row r="36" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B36" s="46">
-        <v>31</v>
-      </c>
-      <c r="C36" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="D36" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="46">
-        <v>21</v>
-      </c>
-      <c r="G36" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J36" s="47"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="46">
-        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="O36" s="46">
-        <v>10</v>
-      </c>
-      <c r="P36" s="46"/>
-      <c r="Q36" s="46"/>
-      <c r="R36" s="46"/>
-      <c r="S36" s="46">
-        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
-        <v>12</v>
-      </c>
-      <c r="T36" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="U36" s="47"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="47"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="47"/>
-      <c r="Z36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="46">
-        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>1</v>
-      </c>
-      <c r="AC36" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD36" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE36" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
-        <v>0</v>
-      </c>
-      <c r="AF36" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
-        <v>0</v>
-      </c>
-      <c r="AG36" s="46">
-        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>1</v>
-      </c>
-      <c r="AH36" s="46">
-        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>13</v>
-      </c>
-      <c r="AI36" s="44"/>
-    </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B37" s="46">
-        <v>32</v>
-      </c>
-      <c r="C37" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F37" s="46">
-        <v>19</v>
-      </c>
-      <c r="G37" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="J37" s="47"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="47"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="46">
-        <f>COUNTA(Список35[[#This Row],[02.сен]:[25.дек]])</f>
-        <v>3</v>
-      </c>
-      <c r="O37" s="46">
-        <v>10</v>
-      </c>
-      <c r="P37" s="46"/>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46">
-        <f>Список35[[#This Row],[Лекции]]+Список35[[#This Row],[РК1]]+Список35[[#This Row],[РК2]]+Список35[[#This Row],[РК3]]+Список35[[#This Row],[ДЗ]]</f>
-        <v>13</v>
-      </c>
-      <c r="T37" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="U37" s="47">
-        <v>1</v>
-      </c>
-      <c r="V37" s="34"/>
-      <c r="W37" s="47"/>
-      <c r="X37" s="34"/>
-      <c r="Y37" s="47"/>
-      <c r="Z37" s="34"/>
-      <c r="AA37" s="34"/>
-      <c r="AB37" s="46">
-        <f>COUNTA(Список35[[#This Row],[09.сен]:[30.дек]])</f>
-        <v>2</v>
-      </c>
-      <c r="AC37" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],1)*AC$3</f>
-        <v>8</v>
-      </c>
-      <c r="AD37" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],2)*AD$3</f>
-        <v>0</v>
-      </c>
-      <c r="AE37" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],3)*AE$3</f>
-        <v>0</v>
-      </c>
-      <c r="AF37" s="46">
-        <f>COUNTIF(Список35[[#This Row],[09.сен]:[30.дек]],4)*AF$3</f>
-        <v>0</v>
-      </c>
-      <c r="AG37" s="46">
-        <f>SUM(Список35[[#This Row],[Лабы]:[Отч4]])</f>
-        <v>10</v>
-      </c>
-      <c r="AH37" s="46">
-        <f>Список35[[#This Row],[Теория]]+Список35[[#This Row],[Практика]]</f>
-        <v>23</v>
-      </c>
-      <c r="AI37" s="45" t="s">
+      <c r="AI37" s="41" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="38" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="34">
         <f>COUNTA(Список35[02.сен])</f>
         <v>31</v>
@@ -5933,78 +5898,75 @@
         <f>COUNTA(Список35[25.дек])</f>
         <v>0</v>
       </c>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46">
+      <c r="N38" s="40"/>
+      <c r="O38" s="40">
         <f>SUBTOTAL(102,Список35[РК1])</f>
         <v>31</v>
       </c>
-      <c r="P38" s="46">
+      <c r="P38" s="40">
         <f>SUBTOTAL(102,Список35[РК2])</f>
         <v>0</v>
       </c>
-      <c r="Q38" s="46">
+      <c r="Q38" s="40">
         <f>SUBTOTAL(102,Список35[РК3])</f>
         <v>0</v>
       </c>
-      <c r="R38" s="46">
+      <c r="R38" s="40">
         <f>SUBTOTAL(102,Список35[ДЗ])</f>
         <v>0</v>
       </c>
-      <c r="S38" s="46"/>
-      <c r="T38" s="46">
+      <c r="S38" s="40"/>
+      <c r="T38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="U38" s="46">
+      <c r="U38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="V38" s="46">
+      <c r="V38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="W38" s="46">
+      <c r="W38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="X38" s="46">
+      <c r="X38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="Y38" s="46">
+      <c r="Y38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="Z38" s="46">
+      <c r="Z38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="AA38" s="46">
+      <c r="AA38" s="40">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="AB38" s="46"/>
-      <c r="AC38" s="46">
+      <c r="AB38" s="40"/>
+      <c r="AC38" s="40">
         <f>COUNTIF(Список35[Отч1],"&lt;&gt;0")</f>
-        <v>13</v>
-      </c>
-      <c r="AD38" s="46">
+        <v>22</v>
+      </c>
+      <c r="AD38" s="40">
         <f>COUNTIF(Список35[Отч2],"&lt;&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="AE38" s="46">
+        <v>4</v>
+      </c>
+      <c r="AE38" s="40">
         <f>COUNTIF(Список35[Отч3],"&lt;&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AF38" s="46">
+      <c r="AF38" s="40">
         <f>COUNTIF(Список35[Отч4],"&lt;&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AG38" s="46"/>
-      <c r="AH38" s="46">
-        <f>SUBTOTAL(103,Список35[Итог])</f>
-        <v>32</v>
-      </c>
+      <c r="AG38" s="40"/>
+      <c r="AH38" s="40"/>
       <c r="AI38">
         <f>SUBTOTAL(103,Список35[Книги])</f>
         <v>14</v>
@@ -6016,9 +5978,9 @@
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="22"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="11"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
@@ -6036,33 +5998,8 @@
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="N38:N39">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N40:N41">
+  <conditionalFormatting sqref="N39:N40">
     <cfRule type="dataBar" priority="12">
       <dataBar>
         <cfvo type="min"/>
@@ -6128,6 +6065,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N38">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
@@ -6145,7 +6094,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N40:N41</xm:sqref>
+          <xm:sqref>N39:N40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{F77FC200-5913-4B1A-A214-2B631C5DD913}">
@@ -6660,33 +6609,33 @@
     <col min="19" max="19" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C1" s="23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="2:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G2" s="38" t="s">
+    <row r="2" spans="2:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="39" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="40" t="s">
+      <c r="J2" s="45"/>
+      <c r="K2" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="41"/>
-      <c r="M2" s="39" t="s">
+      <c r="L2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="38"/>
+      <c r="N2" s="45"/>
       <c r="P2" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="2:20" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:20" ht="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
